--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F439"/>
+  <dimension ref="A1:F440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10966,6 +10966,30 @@
       <c r="F439" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>475.3</v>
+      </c>
+      <c r="C440" t="n">
+        <v>379</v>
+      </c>
+      <c r="D440" t="n">
+        <v>383.24</v>
+      </c>
+      <c r="E440" t="n">
+        <v>406.43</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10980,7 +11004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B493"/>
+  <dimension ref="A1:B494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15913,6 +15937,16 @@
       </c>
       <c r="B493" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -16081,28 +16115,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.701558653377822</v>
+        <v>6.718577504410965</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6382210551575693</v>
+        <v>0.6401328211647912</v>
       </c>
       <c r="M2" t="n">
-        <v>31.35490366714641</v>
+        <v>31.39492321743118</v>
       </c>
       <c r="N2" t="n">
-        <v>1435.859032244234</v>
+        <v>1435.621746461652</v>
       </c>
       <c r="O2" t="n">
-        <v>37.89273059894516</v>
+        <v>37.88959944973886</v>
       </c>
       <c r="P2" t="n">
-        <v>262.8071731443552</v>
+        <v>262.6396235822652</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16159,28 +16193,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.393224437766424</v>
+        <v>3.396845286968758</v>
       </c>
       <c r="J3" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K3" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8958967814322436</v>
+        <v>0.8964180999768571</v>
       </c>
       <c r="M3" t="n">
-        <v>7.301803930325266</v>
+        <v>7.298373554671342</v>
       </c>
       <c r="N3" t="n">
-        <v>75.06673597867238</v>
+        <v>75.0341756500501</v>
       </c>
       <c r="O3" t="n">
-        <v>8.66410618463742</v>
+        <v>8.662226945194297</v>
       </c>
       <c r="P3" t="n">
-        <v>282.1404242543445</v>
+        <v>282.1046321033724</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16237,28 +16271,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.609115263022631</v>
+        <v>3.61134528183239</v>
       </c>
       <c r="J4" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K4" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8892914773852729</v>
+        <v>0.8898781404123848</v>
       </c>
       <c r="M4" t="n">
-        <v>7.8206118623118</v>
+        <v>7.808718123844576</v>
       </c>
       <c r="N4" t="n">
-        <v>90.98181768558365</v>
+        <v>90.82707963264063</v>
       </c>
       <c r="O4" t="n">
-        <v>9.538438954335435</v>
+        <v>9.5303242144557</v>
       </c>
       <c r="P4" t="n">
-        <v>283.7231817996733</v>
+        <v>283.7011380288756</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16315,28 +16349,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.396869968723252</v>
+        <v>4.395782623432614</v>
       </c>
       <c r="J5" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K5" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8000903300132667</v>
+        <v>0.800852947713427</v>
       </c>
       <c r="M5" t="n">
-        <v>13.54440662297071</v>
+        <v>13.51854025864787</v>
       </c>
       <c r="N5" t="n">
-        <v>271.0180429193372</v>
+        <v>270.4131738815146</v>
       </c>
       <c r="O5" t="n">
-        <v>16.4626256386804</v>
+        <v>16.4442443998353</v>
       </c>
       <c r="P5" t="n">
-        <v>293.4100208183115</v>
+        <v>293.4207692435087</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16374,7 +16408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F439"/>
+  <dimension ref="A1:F440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30413,6 +30447,38 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-41.86864691837042,174.16221126866822</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-41.86879932491072,174.16077281470513</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-41.869385425395905,174.16059667948278</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-41.87003545553775,174.16079289455547</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F440"/>
+  <dimension ref="A1:F441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10990,6 +10990,30 @@
       <c r="F440" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>475.3</v>
+      </c>
+      <c r="C441" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="D441" t="n">
+        <v>383.48</v>
+      </c>
+      <c r="E441" t="n">
+        <v>406.16</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11004,7 +11028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B494"/>
+  <dimension ref="A1:B495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15947,6 +15971,16 @@
       </c>
       <c r="B494" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -16115,28 +16149,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.718577504410965</v>
+        <v>6.73522958711793</v>
       </c>
       <c r="J2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6401328211647912</v>
+        <v>0.6420340688292258</v>
       </c>
       <c r="M2" t="n">
-        <v>31.39492321743118</v>
+        <v>31.43187427022928</v>
       </c>
       <c r="N2" t="n">
-        <v>1435.621746461652</v>
+        <v>1435.266814060131</v>
       </c>
       <c r="O2" t="n">
-        <v>37.88959944973886</v>
+        <v>37.88491538937537</v>
       </c>
       <c r="P2" t="n">
-        <v>262.6396235822652</v>
+        <v>262.4752158955077</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16193,28 +16227,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.396845286968758</v>
+        <v>3.400438633766906</v>
       </c>
       <c r="J3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8964180999768571</v>
+        <v>0.8969384474445494</v>
       </c>
       <c r="M3" t="n">
-        <v>7.298373554671342</v>
+        <v>7.294872523790207</v>
       </c>
       <c r="N3" t="n">
-        <v>75.0341756500501</v>
+        <v>75.00018177229167</v>
       </c>
       <c r="O3" t="n">
-        <v>8.662226945194297</v>
+        <v>8.660264532466181</v>
       </c>
       <c r="P3" t="n">
-        <v>282.1046321033724</v>
+        <v>282.069010713293</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16271,28 +16305,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.61134528183239</v>
+        <v>3.613551832923161</v>
       </c>
       <c r="J4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8898781404123848</v>
+        <v>0.8904625661243223</v>
       </c>
       <c r="M4" t="n">
-        <v>7.808718123844576</v>
+        <v>7.796768308012145</v>
       </c>
       <c r="N4" t="n">
-        <v>90.82707963264063</v>
+        <v>90.67213987943677</v>
       </c>
       <c r="O4" t="n">
-        <v>9.5303242144557</v>
+        <v>9.522191968209672</v>
       </c>
       <c r="P4" t="n">
-        <v>283.7011380288756</v>
+        <v>283.6792641543097</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16349,28 +16383,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.395782623432614</v>
+        <v>4.394444190491991</v>
       </c>
       <c r="J5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
-        <v>0.800852947713427</v>
+        <v>0.8015927043506408</v>
       </c>
       <c r="M5" t="n">
-        <v>13.51854025864787</v>
+        <v>13.49390061253358</v>
       </c>
       <c r="N5" t="n">
-        <v>270.4131738815146</v>
+        <v>269.8175415222861</v>
       </c>
       <c r="O5" t="n">
-        <v>16.4442443998353</v>
+        <v>16.42612375219078</v>
       </c>
       <c r="P5" t="n">
-        <v>293.4207692435087</v>
+        <v>293.4340373316034</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16408,7 +16442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F440"/>
+  <dimension ref="A1:F441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30479,6 +30513,38 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-41.86864691837042,174.16221126866822</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-41.868800129851934,174.16077549836595</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-41.8693858114625,174.1605995246768</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-41.87003524128608,174.16078965401644</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F441"/>
+  <dimension ref="A1:F442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11014,6 +11014,30 @@
       <c r="F441" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>472.98</v>
+      </c>
+      <c r="C442" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="D442" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="E442" t="n">
+        <v>404.35</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B495"/>
+  <dimension ref="A1:B496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15981,6 +16005,16 @@
       </c>
       <c r="B495" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -16149,28 +16183,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.73522958711793</v>
+        <v>6.750284256004987</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K2" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6420340688292258</v>
+        <v>0.6439305304325624</v>
       </c>
       <c r="M2" t="n">
-        <v>31.43187427022928</v>
+        <v>31.45724809676876</v>
       </c>
       <c r="N2" t="n">
-        <v>1435.266814060131</v>
+        <v>1434.353074653448</v>
       </c>
       <c r="O2" t="n">
-        <v>37.88491538937537</v>
+        <v>37.87285406004475</v>
       </c>
       <c r="P2" t="n">
-        <v>262.4752158955077</v>
+        <v>262.3256015502755</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16227,28 +16261,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.400438633766906</v>
+        <v>3.40306741606159</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K3" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8969384474445494</v>
+        <v>0.8974914020258213</v>
       </c>
       <c r="M3" t="n">
-        <v>7.294872523790207</v>
+        <v>7.287802675090668</v>
       </c>
       <c r="N3" t="n">
-        <v>75.00018177229167</v>
+        <v>74.90220492199174</v>
       </c>
       <c r="O3" t="n">
-        <v>8.660264532466181</v>
+        <v>8.654605994613027</v>
       </c>
       <c r="P3" t="n">
-        <v>282.069010713293</v>
+        <v>282.0427805762007</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16305,28 +16339,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.613551832923161</v>
+        <v>3.615161347327168</v>
       </c>
       <c r="J4" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8904625661243223</v>
+        <v>0.891046951113123</v>
       </c>
       <c r="M4" t="n">
-        <v>7.796768308012145</v>
+        <v>7.783227108851572</v>
       </c>
       <c r="N4" t="n">
-        <v>90.67213987943677</v>
+        <v>90.49355908206788</v>
       </c>
       <c r="O4" t="n">
-        <v>9.522191968209672</v>
+        <v>9.512810262065983</v>
       </c>
       <c r="P4" t="n">
-        <v>283.6792641543097</v>
+        <v>283.6632043293654</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16383,28 +16417,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.394444190491991</v>
+        <v>4.391959077860339</v>
       </c>
       <c r="J5" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K5" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8015927043506408</v>
+        <v>0.8022348926503136</v>
       </c>
       <c r="M5" t="n">
-        <v>13.49390061253358</v>
+        <v>13.47440381108444</v>
       </c>
       <c r="N5" t="n">
-        <v>269.8175415222861</v>
+        <v>269.2701373031902</v>
       </c>
       <c r="O5" t="n">
-        <v>16.42612375219078</v>
+        <v>16.40945268140257</v>
       </c>
       <c r="P5" t="n">
-        <v>293.4340373316034</v>
+        <v>293.4588339247447</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16442,7 +16476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F441"/>
+  <dimension ref="A1:F442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30545,6 +30579,38 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-41.8686370894668,174.16218660209057</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-41.868794964811336,174.16075827821012</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-41.86938463717639,174.16059087054504</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-41.87003380500405,174.16076793040355</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F442"/>
+  <dimension ref="A1:F443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11036,6 +11036,30 @@
         <v>404.35</v>
       </c>
       <c r="F442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>481.39</v>
+      </c>
+      <c r="C443" t="n">
+        <v>376.76</v>
+      </c>
+      <c r="D443" t="n">
+        <v>381.35</v>
+      </c>
+      <c r="E443" t="n">
+        <v>404.5</v>
+      </c>
+      <c r="F443" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11052,7 +11076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B496"/>
+  <dimension ref="A1:B497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16015,6 +16039,16 @@
       </c>
       <c r="B496" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -16183,28 +16217,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.750284256004987</v>
+        <v>6.768864557833604</v>
       </c>
       <c r="J2" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6439305304325624</v>
+        <v>0.6458683774956353</v>
       </c>
       <c r="M2" t="n">
-        <v>31.45724809676876</v>
+        <v>31.50451095655108</v>
       </c>
       <c r="N2" t="n">
-        <v>1434.353074653448</v>
+        <v>1434.678785961</v>
       </c>
       <c r="O2" t="n">
-        <v>37.87285406004475</v>
+        <v>37.87715387883572</v>
       </c>
       <c r="P2" t="n">
-        <v>262.3256015502755</v>
+        <v>262.1402683526714</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16261,28 +16295,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.40306741606159</v>
+        <v>3.40509835026207</v>
       </c>
       <c r="J3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8974914020258213</v>
+        <v>0.8980475631080787</v>
       </c>
       <c r="M3" t="n">
-        <v>7.287802675090668</v>
+        <v>7.278611274732159</v>
       </c>
       <c r="N3" t="n">
-        <v>74.90220492199174</v>
+        <v>74.77568967996726</v>
       </c>
       <c r="O3" t="n">
-        <v>8.654605994613027</v>
+        <v>8.647293777822473</v>
       </c>
       <c r="P3" t="n">
-        <v>282.0427805762007</v>
+        <v>282.0224414583458</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16339,28 +16373,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.615161347327168</v>
+        <v>3.61595832573403</v>
       </c>
       <c r="J4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.891046951113123</v>
+        <v>0.8916095891818363</v>
       </c>
       <c r="M4" t="n">
-        <v>7.783227108851572</v>
+        <v>7.767640192399859</v>
       </c>
       <c r="N4" t="n">
-        <v>90.49355908206788</v>
+        <v>90.2954360299359</v>
       </c>
       <c r="O4" t="n">
-        <v>9.512810262065983</v>
+        <v>9.502391069090763</v>
       </c>
       <c r="P4" t="n">
-        <v>283.6632043293654</v>
+        <v>283.6552228606693</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16417,28 +16451,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.391959077860339</v>
+        <v>4.389382551744896</v>
       </c>
       <c r="J5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8022348926503136</v>
+        <v>0.8028703498525578</v>
       </c>
       <c r="M5" t="n">
-        <v>13.47440381108444</v>
+        <v>13.45532663155883</v>
       </c>
       <c r="N5" t="n">
-        <v>269.2701373031902</v>
+        <v>268.7300494951695</v>
       </c>
       <c r="O5" t="n">
-        <v>16.40945268140257</v>
+        <v>16.39298781476914</v>
       </c>
       <c r="P5" t="n">
-        <v>293.4588339247447</v>
+        <v>293.4846369607592</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16476,7 +16510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F442"/>
+  <dimension ref="A1:F443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30611,6 +30645,38 @@
         </is>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-41.86867271921671,174.1622760184701</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-41.86879181212292,174.16074776720725</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-41.869382385118996,174.16057427358086</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-41.8700339240331,174.16076973070295</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F443"/>
+  <dimension ref="A1:F445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11060,6 +11060,54 @@
         <v>404.5</v>
       </c>
       <c r="F443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>481.91</v>
+      </c>
+      <c r="C444" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="D444" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="E444" t="n">
+        <v>404.5</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>481.91</v>
+      </c>
+      <c r="C445" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="D445" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="E445" t="n">
+        <v>403.39</v>
+      </c>
+      <c r="F445" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11076,7 +11124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B497"/>
+  <dimension ref="A1:B499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16049,6 +16097,26 @@
       </c>
       <c r="B497" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -16217,28 +16285,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.768864557833604</v>
+        <v>6.805406752780383</v>
       </c>
       <c r="J2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6458683774956353</v>
+        <v>0.6497037392758467</v>
       </c>
       <c r="M2" t="n">
-        <v>31.50451095655108</v>
+        <v>31.5938619990514</v>
       </c>
       <c r="N2" t="n">
-        <v>1434.678785961</v>
+        <v>1435.160226542725</v>
       </c>
       <c r="O2" t="n">
-        <v>37.87715387883572</v>
+        <v>37.88350863558872</v>
       </c>
       <c r="P2" t="n">
-        <v>262.1402683526714</v>
+        <v>261.7746063896082</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16295,28 +16363,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.40509835026207</v>
+        <v>3.408780206765679</v>
       </c>
       <c r="J3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8980475631080787</v>
+        <v>0.8991474133704596</v>
       </c>
       <c r="M3" t="n">
-        <v>7.278611274732159</v>
+        <v>7.259032066369068</v>
       </c>
       <c r="N3" t="n">
-        <v>74.77568967996726</v>
+        <v>74.50984789573134</v>
       </c>
       <c r="O3" t="n">
-        <v>8.647293777822473</v>
+        <v>8.631908705247719</v>
       </c>
       <c r="P3" t="n">
-        <v>282.0224414583458</v>
+        <v>281.9854520370597</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16373,28 +16441,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.61595832573403</v>
+        <v>3.617417823956279</v>
       </c>
       <c r="J4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8916095891818363</v>
+        <v>0.8927202641352197</v>
       </c>
       <c r="M4" t="n">
-        <v>7.767640192399859</v>
+        <v>7.736302114591846</v>
       </c>
       <c r="N4" t="n">
-        <v>90.2954360299359</v>
+        <v>89.8998954439059</v>
       </c>
       <c r="O4" t="n">
-        <v>9.502391069090763</v>
+        <v>9.481555539251241</v>
       </c>
       <c r="P4" t="n">
-        <v>283.6552228606693</v>
+        <v>283.6405604477571</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16451,28 +16519,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.389382551744896</v>
+        <v>4.38349433740256</v>
       </c>
       <c r="J5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8028703498525578</v>
+        <v>0.8040536261025153</v>
       </c>
       <c r="M5" t="n">
-        <v>13.45532663155883</v>
+        <v>13.42073988668109</v>
       </c>
       <c r="N5" t="n">
-        <v>268.7300494951695</v>
+        <v>267.70263857959</v>
       </c>
       <c r="O5" t="n">
-        <v>16.39298781476914</v>
+        <v>16.36162090318652</v>
       </c>
       <c r="P5" t="n">
-        <v>293.4846369607592</v>
+        <v>293.5437953695923</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16510,7 +16578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F443"/>
+  <dimension ref="A1:F445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30677,6 +30745,70 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-41.8686749222429,174.16228154719118</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-41.86879164442669,174.1607472081114</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-41.86938273901388,174.16057688167518</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-41.8700339240331,174.16076973070295</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-41.8686749222429,174.16228154719118</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-41.86879140965198,174.16074642537717</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-41.8693825459803,174.16057545907827</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-41.870033043217425,174.16075640848769</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F445"/>
+  <dimension ref="A1:F449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11108,6 +11108,102 @@
         <v>403.39</v>
       </c>
       <c r="F445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>478.17</v>
+      </c>
+      <c r="C446" t="n">
+        <v>375.85</v>
+      </c>
+      <c r="D446" t="n">
+        <v>380.64</v>
+      </c>
+      <c r="E446" t="n">
+        <v>408.77</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>481.51</v>
+      </c>
+      <c r="C447" t="n">
+        <v>376.07</v>
+      </c>
+      <c r="D447" t="n">
+        <v>379.96</v>
+      </c>
+      <c r="E447" t="n">
+        <v>412.88</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>464.42</v>
+      </c>
+      <c r="C448" t="n">
+        <v>375.23</v>
+      </c>
+      <c r="D448" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="E448" t="n">
+        <v>412.78</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>453.01</v>
+      </c>
+      <c r="C449" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="D449" t="n">
+        <v>379.12</v>
+      </c>
+      <c r="E449" t="n">
+        <v>410.7</v>
+      </c>
+      <c r="F449" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11124,7 +11220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B499"/>
+  <dimension ref="A1:B503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16117,6 +16213,46 @@
       </c>
       <c r="B499" t="n">
         <v>0.58</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -16285,28 +16421,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.805406752780383</v>
+        <v>6.851996008445971</v>
       </c>
       <c r="J2" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K2" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6497037392758467</v>
+        <v>0.6565360678453497</v>
       </c>
       <c r="M2" t="n">
-        <v>31.5938619990514</v>
+        <v>31.60594373962875</v>
       </c>
       <c r="N2" t="n">
-        <v>1435.160226542725</v>
+        <v>1429.290215412535</v>
       </c>
       <c r="O2" t="n">
-        <v>37.88350863558872</v>
+        <v>37.80595476128774</v>
       </c>
       <c r="P2" t="n">
-        <v>261.7746063896082</v>
+        <v>261.3073292190558</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16363,28 +16499,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.408780206765679</v>
+        <v>3.412910908979426</v>
       </c>
       <c r="J3" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K3" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8991474133704596</v>
+        <v>0.901216513269962</v>
       </c>
       <c r="M3" t="n">
-        <v>7.259032066369068</v>
+        <v>7.208899967465361</v>
       </c>
       <c r="N3" t="n">
-        <v>74.50984789573134</v>
+        <v>73.8979943051943</v>
       </c>
       <c r="O3" t="n">
-        <v>8.631908705247719</v>
+        <v>8.596394261851552</v>
       </c>
       <c r="P3" t="n">
-        <v>281.9854520370597</v>
+        <v>281.9438555189901</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16441,28 +16577,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.617417823956279</v>
+        <v>3.616788338911729</v>
       </c>
       <c r="J4" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K4" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8927202641352197</v>
+        <v>0.8947081220639455</v>
       </c>
       <c r="M4" t="n">
-        <v>7.736302114591846</v>
+        <v>7.674354393706243</v>
       </c>
       <c r="N4" t="n">
-        <v>89.8998954439059</v>
+        <v>89.10195171442385</v>
       </c>
       <c r="O4" t="n">
-        <v>9.481555539251241</v>
+        <v>9.439383015559006</v>
       </c>
       <c r="P4" t="n">
-        <v>283.6405604477571</v>
+        <v>283.646913765618</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16519,28 +16655,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.38349433740256</v>
+        <v>4.384847699174806</v>
       </c>
       <c r="J5" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K5" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8040536261025153</v>
+        <v>0.80747107334527</v>
       </c>
       <c r="M5" t="n">
-        <v>13.42073988668109</v>
+        <v>13.31537863090228</v>
       </c>
       <c r="N5" t="n">
-        <v>267.70263857959</v>
+        <v>265.3417450234516</v>
       </c>
       <c r="O5" t="n">
-        <v>16.36162090318652</v>
+        <v>16.28931382911667</v>
       </c>
       <c r="P5" t="n">
-        <v>293.5437953695923</v>
+        <v>293.5301518504023</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16578,7 +16714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F445"/>
+  <dimension ref="A1:F449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30809,6 +30945,134 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-41.86865907739458,174.16224178293623</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-41.86878876005129,174.1607375916629</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-41.86938124300324,174.16056585654948</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-41.870037312381655,174.16082097922774</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-41.8686732276074,174.16227729432876</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-41.86878949791484,174.16074005168454</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-41.869380149145314,174.16055779516753</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-41.87004057374463,174.16087030743773</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-41.86860082415487,174.16209559098945</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-41.86878668061734,174.16073065887497</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-41.869379602216135,174.16055376447667</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-41.87004049439299,174.16086910723794</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-41.868552484413094,174.16197427845324</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-41.86878221989471,174.16071578692817</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-41.86937879790828,174.16054783699025</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-41.87003884387591,174.16084414308247</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0375/nzd0375.xlsx
+++ b/data/nzd0375/nzd0375.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F449"/>
+  <dimension ref="A1:F451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11204,6 +11204,54 @@
         <v>410.7</v>
       </c>
       <c r="F449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>427.14</v>
+      </c>
+      <c r="C450" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="D450" t="n">
+        <v>379.06</v>
+      </c>
+      <c r="E450" t="n">
+        <v>407.97</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>411.34</v>
+      </c>
+      <c r="C451" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="D451" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="E451" t="n">
+        <v>402.77</v>
+      </c>
+      <c r="F451" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11220,7 +11268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B503"/>
+  <dimension ref="A1:B505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16253,6 +16301,26 @@
       </c>
       <c r="B503" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -16421,28 +16489,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.851996008445971</v>
+        <v>6.829057128691369</v>
       </c>
       <c r="J2" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K2" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6565360678453497</v>
+        <v>0.656907314914519</v>
       </c>
       <c r="M2" t="n">
-        <v>31.60594373962875</v>
+        <v>31.54595824290756</v>
       </c>
       <c r="N2" t="n">
-        <v>1429.290215412535</v>
+        <v>1426.076417901698</v>
       </c>
       <c r="O2" t="n">
-        <v>37.80595476128774</v>
+        <v>37.76342698831368</v>
       </c>
       <c r="P2" t="n">
-        <v>261.3073292190558</v>
+        <v>261.5385233110309</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16499,28 +16567,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.412910908979426</v>
+        <v>3.402672176869107</v>
       </c>
       <c r="J3" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K3" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L3" t="n">
-        <v>0.901216513269962</v>
+        <v>0.9008131055189983</v>
       </c>
       <c r="M3" t="n">
-        <v>7.208899967465361</v>
+        <v>7.241715204223171</v>
       </c>
       <c r="N3" t="n">
-        <v>73.8979943051943</v>
+        <v>74.2381134108346</v>
       </c>
       <c r="O3" t="n">
-        <v>8.596394261851552</v>
+        <v>8.616154212340597</v>
       </c>
       <c r="P3" t="n">
-        <v>281.9438555189901</v>
+        <v>282.0474642689373</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16577,28 +16645,28 @@
         <v>0.1297</v>
       </c>
       <c r="I4" t="n">
-        <v>3.616788338911729</v>
+        <v>3.61513576250742</v>
       </c>
       <c r="J4" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8947081220639455</v>
+        <v>0.8955939766567759</v>
       </c>
       <c r="M4" t="n">
-        <v>7.674354393706243</v>
+        <v>7.652102597914521</v>
       </c>
       <c r="N4" t="n">
-        <v>89.10195171442385</v>
+        <v>88.72187741571636</v>
       </c>
       <c r="O4" t="n">
-        <v>9.439383015559006</v>
+        <v>9.419229130651635</v>
       </c>
       <c r="P4" t="n">
-        <v>283.646913765618</v>
+        <v>283.6636343352895</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16655,28 +16723,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>4.384847699174806</v>
+        <v>4.37983210737293</v>
       </c>
       <c r="J5" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K5" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L5" t="n">
-        <v>0.80747107334527</v>
+        <v>0.8086495566722953</v>
       </c>
       <c r="M5" t="n">
-        <v>13.31537863090228</v>
+        <v>13.27882548204136</v>
       </c>
       <c r="N5" t="n">
-        <v>265.3417450234516</v>
+        <v>264.332860568102</v>
       </c>
       <c r="O5" t="n">
-        <v>16.28931382911667</v>
+        <v>16.25831665850134</v>
       </c>
       <c r="P5" t="n">
-        <v>293.5301518504023</v>
+        <v>293.5809099085087</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16714,7 +16782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F449"/>
+  <dimension ref="A1:F451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31073,6 +31141,70 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>-41.868442882778496,174.16169922607176</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>-41.86875703186781,174.16063181078553</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-41.86937870139133,174.1605471256919</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-41.870036677563995,174.1608113776302</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-41.868375943683496,174.16153123937656</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-41.86872687994002,174.16053128550158</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-41.869377478842715,174.16053811591277</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-41.87003255122963,174.1607489672505</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
